--- a/Docs/Test-Case/Test_Case_Authorization.xlsx
+++ b/Docs/Test-Case/Test_Case_Authorization.xlsx
@@ -1,43 +1,619 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>TC-AUTH-01</t>
+  </si>
+  <si>
+    <t>Đăng ký tài khoản với role MANAGER (Lỗ hổng bảo mật)</t>
+  </si>
+  <si>
+    <t>Guest (Chưa đăng nhập)</t>
+  </si>
+  <si>
+    <t>Body: {"email": "test@...", "password": "123", "role": "ROLE_MANAGER"}</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối tạo tài khoản hoặc tự động ép role về CUSTOMER.</t>
+  </si>
+  <si>
+    <t>TC-AUTH-02</t>
+  </si>
+  <si>
+    <t>Truy cập API tạo sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>POST /seller/product/new</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về lỗi 401 Unauthorized.</t>
+  </si>
+  <si>
+    <t>TC-AUTH-03</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm mới bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Đăng nhập với role Customer</t>
+  </si>
+  <si>
+    <t>Token của Customer, Body: ProductInfo hợp lệ</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về lỗi 403 Forbidden.</t>
+  </si>
+  <si>
+    <t>TC-AUTH-04</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm mới bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Đăng nhập với role Employee</t>
+  </si>
+  <si>
+    <t>Token của Employee, Body: ProductInfo hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-05</t>
+  </si>
+  <si>
+    <t>Truy cập API sửa sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>PUT /seller/product/{id}/edit</t>
+  </si>
+  <si>
+    <t>TC-AUTH-06</t>
+  </si>
+  <si>
+    <t>Sửa thông tin sản phẩm bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>Token của Customer, id hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-07</t>
+  </si>
+  <si>
+    <t>Truy cập API xóa sản phẩm khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>DELETE /seller/product/{id}/delete</t>
+  </si>
+  <si>
+    <t>TC-AUTH-08</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>TC-AUTH-09</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>Token của Employee, id hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-10</t>
+  </si>
+  <si>
+    <t>Xem giỏ hàng của user trên server khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>GET /cart</t>
+  </si>
+  <si>
+    <t>TC-AUTH-11</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ hàng bằng tài khoản Employee</t>
+  </si>
+  <si>
+    <t>POST /cart/add, productId hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-AUTH-12</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ hàng bằng tài khoản Manager</t>
+  </si>
+  <si>
+    <t>Đăng nhập với role Manager</t>
+  </si>
+  <si>
+    <t>TC-AUTH-13</t>
+  </si>
+  <si>
+    <t>Gọi API Checkout (đặt hàng) khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>POST /cart/checkout</t>
+  </si>
+  <si>
+    <t>TC-AUTH-14</t>
+  </si>
+  <si>
+    <t>Xem danh sách đơn hàng khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>GET /order</t>
+  </si>
+  <si>
+    <t>TC-AUTH-15</t>
+  </si>
+  <si>
+    <t>Xem chi tiết đơn hàng của người khác (Customer A xem của B)</t>
+  </si>
+  <si>
+    <t>Đăng nhập với role Customer (A)</t>
+  </si>
+  <si>
+    <t>GET /order/{id} (ID thuộc về Customer B)</t>
+  </si>
+  <si>
+    <t>Hệ thống trả lỗi 403 Forbidden hoặc 401 Unauthorized.</t>
+  </si>
+  <si>
+    <t>TC-AUTH-16</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng của người khác (Customer A hủy của B)</t>
+  </si>
+  <si>
+    <t>PATCH /order/cancel/{id} (ID của B)</t>
+  </si>
+  <si>
+    <t>TC-AUTH-17</t>
+  </si>
+  <si>
+    <t>Xác nhận hoàn tất đơn hàng khi chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>PATCH /order/finish/{id}</t>
+  </si>
+  <si>
+    <t>TC-AUTH-18</t>
+  </si>
+  <si>
+    <t>Xác nhận hoàn tất đơn hàng bằng tài khoản Customer</t>
+  </si>
+  <si>
+    <t>TC-AUTH-19</t>
+  </si>
+  <si>
+    <t>Truy cập API xem toàn bộ đơn hàng hệ thống bằng Customer</t>
+  </si>
+  <si>
+    <t>GET /order/all</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,24 +621,331 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -111,7 +994,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -146,7 +1029,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -320,20 +1203,379 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" ht="28.35" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="138.75" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" ht="97.35" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="97.35" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="97.35" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="97.35" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" ht="111.15" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="97.35" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="83.55" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="83.55" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="97.35" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="124.95" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="111.15" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" ht="97.35" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" ht="111.15" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="111.15" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" ht="111.15" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" ht="111.15" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" ht="124.95" spans="1:6">
+      <c r="A19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" ht="124.95" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Docs/Test-Case/Test_Case_Authorization.xlsx
+++ b/Docs/Test-Case/Test_Case_Authorization.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1497,6 +1497,313 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>BOUNDARY VALUE ANALYSIS (BVA) - API LEVEL</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_01</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra đăng ký với Password có độ dài 2 ký tự (giá trị dưới biên)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>API /register hoạt động; Email chưa tồn tại.</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /register.
+2. Nhập Password: 12.
+3. Nhập các thông tin User hợp lệ khác.
+4. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request do Password phải có tối thiểu 3 ký tự.</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>NG – API trả 200 OK</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>BUG-BVA-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_02</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra đăng ký với Password = 3 ký tự</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>API đăng ký hoạt động, email chưa tồn tại.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /register.
+2. Nhập Password: 123.
+3. Nhập các thông tin User hợp lệ khác.
+4. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_03</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra thêm sản phẩm vào giỏ hàng với Quantity = 0</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập Customer hợp lệ, sản phẩm tồn tại.</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /cart/add.
+2. Nhập body : {"productId": "B0001", "quantity": 0}
+3. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request do Quantity phải ≥ 1.</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>NG – API trả 200 OK, 
+body true</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>BUG-BVA-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_04</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra thêm sản phẩm vào giỏ hàng với Quantity = 1</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập Customer hợp lệ, sản phẩm tồn tại.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /cart/add.
+2. Nhập body : {"productId": "B0001", "quantity": 1}
+3. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, thêm sản phẩm thành công.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK </t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_05</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra tạo sản phẩm với Product Stock = -1</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập tài khoản (Manager) có quyền tạo sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /seller/product/new
+2. Nhập body : 
+{
+  "productId": "B000128",
+  "productName": "Angular in Action",
+  "productPrice": 40.00,
+  "productStock": -1,
+  "productDescription": "Book for learning Angular",
+  "productIcon": "https://via.placeholder.com/150",
+  "categoryType": 0,
+  "productStatus": 0
+}
+3. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request do Product Stock phải ≥ 0.</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>NG – API trả 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>BUG-BVA-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_06</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra tạo sản phẩm với Product Stock = 0</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập tài khoản (Manager) có quyền tạo sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /seller/product/new
+2. Nhập body : 
+{
+  "productId": "B000128",
+  "productName": "Angular in Action",
+  "productPrice": 40.00,
+  "productStock": 1,
+  "productDescription": "Book for learning Angular",
+  "productIcon": "https://via.placeholder.com/150",
+  "categoryType": 0,
+  "productStatus": 0
+}
+3. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK, tạo sản phẩm thành công.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>TC_API_BVA_07</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra tạo sản phẩm với Product Price = -1</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập tài khoản (Manager) có quyền tạo sản phẩm.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>1. Gửi request POST /seller/product/new
+2. Nhập body : 
+{
+  "productId": "B000128",
+  "productName": "Angular in Action",
+  "productPrice": -40.00,
+  "productStock": 50,
+  "productDescription": "Book for learning Angular",
+  "productIcon": "https://via.placeholder.com/150",
+  "categoryType": 0,
+  "productStatus": 0
+}
+3. Gửi request.</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request do giá sản phẩm không được âm.</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>NG – API trả 200 OK</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>BUG-BVA-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
